--- a/docs/Design.xlsx
+++ b/docs/Design.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="880" firstSheet="28" activeTab="36"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="880" firstSheet="32" activeTab="39"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -43,40 +43,45 @@
     <sheet name="BL Draft-outbound" sheetId="54" r:id="rId34"/>
     <sheet name="BL Draft-outbound-Customer" sheetId="56" r:id="rId35"/>
     <sheet name="Awaiting Debit Note" sheetId="58" r:id="rId36"/>
-    <sheet name="Debit note (Other)" sheetId="65" r:id="rId37"/>
-    <sheet name="Receiveable-Payable list" sheetId="60" r:id="rId38"/>
-    <sheet name="Ledger." sheetId="59" r:id="rId39"/>
+    <sheet name="Credit Invoice" sheetId="59" r:id="rId37"/>
+    <sheet name="Debit Invoice" sheetId="65" r:id="rId38"/>
+    <sheet name="Receiveable-Payable list" sheetId="60" r:id="rId39"/>
     <sheet name="Chart of accounts" sheetId="61" r:id="rId40"/>
     <sheet name="Journal" sheetId="62" r:id="rId41"/>
     <sheet name="Expense-Vendor" sheetId="63" r:id="rId42"/>
     <sheet name="Expense-regular" sheetId="64" r:id="rId43"/>
-    <sheet name="sea-airport list" sheetId="15" r:id="rId44"/>
-    <sheet name="cost Head" sheetId="16" r:id="rId45"/>
-    <sheet name="Currency" sheetId="17" r:id="rId46"/>
-    <sheet name="Vessel" sheetId="18" r:id="rId47"/>
-    <sheet name="Carrier" sheetId="19" r:id="rId48"/>
-    <sheet name="Carrier_PIC" sheetId="21" r:id="rId49"/>
-    <sheet name="Carrier Service Port" sheetId="22" r:id="rId50"/>
-    <sheet name="Carrier Service Port_pair" sheetId="33" r:id="rId51"/>
-    <sheet name="Vendor" sheetId="20" r:id="rId52"/>
-    <sheet name="Vendor_Contact_Person" sheetId="23" r:id="rId53"/>
-    <sheet name="Industry_Sector_Catagory" sheetId="24" r:id="rId54"/>
-    <sheet name="Commodity_Catagory_Item_List" sheetId="25" r:id="rId55"/>
-    <sheet name="Local Sales" sheetId="57" r:id="rId56"/>
-    <sheet name="Customer" sheetId="26" r:id="rId57"/>
-    <sheet name="Customer_PIC" sheetId="27" r:id="rId58"/>
-    <sheet name="Agent" sheetId="28" r:id="rId59"/>
-    <sheet name="Agent_PIC" sheetId="29" r:id="rId60"/>
-    <sheet name="Employee" sheetId="30" r:id="rId61"/>
-    <sheet name="Employee_CV" sheetId="31" r:id="rId62"/>
-    <sheet name="Employee_salary" sheetId="32" r:id="rId63"/>
+    <sheet name="Income" sheetId="66" r:id="rId44"/>
+    <sheet name="Income-Other" sheetId="69" r:id="rId45"/>
+    <sheet name="Internal Transfer" sheetId="70" r:id="rId46"/>
+    <sheet name="sea-airport list" sheetId="15" r:id="rId47"/>
+    <sheet name="cost Head" sheetId="16" r:id="rId48"/>
+    <sheet name="Currency" sheetId="17" r:id="rId49"/>
+    <sheet name="Vessel" sheetId="18" r:id="rId50"/>
+    <sheet name="Carrier" sheetId="19" r:id="rId51"/>
+    <sheet name="Carrier_PIC" sheetId="21" r:id="rId52"/>
+    <sheet name="Carrier Service Port" sheetId="22" r:id="rId53"/>
+    <sheet name="Carrier Service Port_pair" sheetId="33" r:id="rId54"/>
+    <sheet name="Vendor" sheetId="20" r:id="rId55"/>
+    <sheet name="Vendor_Contact_Person" sheetId="23" r:id="rId56"/>
+    <sheet name="Industry_Sector_Catagory" sheetId="24" r:id="rId57"/>
+    <sheet name="Commodity_Catagory_Item_List" sheetId="25" r:id="rId58"/>
+    <sheet name="Local Sales" sheetId="57" r:id="rId59"/>
+    <sheet name="Customer" sheetId="26" r:id="rId60"/>
+    <sheet name="Customer_PIC" sheetId="27" r:id="rId61"/>
+    <sheet name="Agent" sheetId="28" r:id="rId62"/>
+    <sheet name="Agent_PIC" sheetId="29" r:id="rId63"/>
+    <sheet name="Employee" sheetId="30" r:id="rId64"/>
+    <sheet name="Employee_CV" sheetId="31" r:id="rId65"/>
+    <sheet name="Employee_salary" sheetId="32" r:id="rId66"/>
+    <sheet name="bank setup" sheetId="67" r:id="rId67"/>
+    <sheet name="Account setup" sheetId="68" r:id="rId68"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3293" uniqueCount="1163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3371" uniqueCount="1199">
   <si>
     <t>Purchase</t>
   </si>
@@ -3085,12 +3090,6 @@
   </si>
   <si>
     <t>Ledger</t>
-  </si>
-  <si>
-    <t>Ledger - CMA</t>
-  </si>
-  <si>
-    <t>Invoice No</t>
   </si>
   <si>
     <t>Descrption</t>
@@ -3812,16 +3811,130 @@
     <t>Create New</t>
   </si>
   <si>
-    <t>Quotation NO</t>
-  </si>
-  <si>
-    <t>Payment Date</t>
-  </si>
-  <si>
     <t xml:space="preserve"> ' + Add</t>
   </si>
   <si>
     <t>- Debit Invoice</t>
+  </si>
+  <si>
+    <t>Income From :</t>
+  </si>
+  <si>
+    <t>( Customer)</t>
+  </si>
+  <si>
+    <t>Deposit to :</t>
+  </si>
+  <si>
+    <t>Income Category</t>
+  </si>
+  <si>
+    <t>Select Income Category</t>
+  </si>
+  <si>
+    <t>Unbilled Amount</t>
+  </si>
+  <si>
+    <t>Unbill Amount(USD)</t>
+  </si>
+  <si>
+    <t>Unbill Amount(Base Cur)</t>
+  </si>
+  <si>
+    <t>Asset = Liabbilities - Owner's Equity</t>
+  </si>
+  <si>
+    <t>Expense Ledger - Predefined</t>
+  </si>
+  <si>
+    <t>Sub Ledger</t>
+  </si>
+  <si>
+    <t>; - Bank Set up</t>
+  </si>
+  <si>
+    <t>Account Name</t>
+  </si>
+  <si>
+    <t>Bank Name</t>
+  </si>
+  <si>
+    <t>Branch</t>
+  </si>
+  <si>
+    <t>Swift No</t>
+  </si>
+  <si>
+    <t>Routing number</t>
+  </si>
+  <si>
+    <t>IBAN No</t>
+  </si>
+  <si>
+    <t>Select Bank</t>
+  </si>
+  <si>
+    <t>Select Branch</t>
+  </si>
+  <si>
+    <t>Account Nuber</t>
+  </si>
+  <si>
+    <t>08633033878</t>
+  </si>
+  <si>
+    <t>Bank Asia Plc</t>
+  </si>
+  <si>
+    <t>Ring Road</t>
+  </si>
+  <si>
+    <t>Ring Road, Mohammadpur , dhaka</t>
+  </si>
+  <si>
+    <t>BAHDD9876</t>
+  </si>
+  <si>
+    <t>07214563</t>
+  </si>
+  <si>
+    <t>Salary for the month of Sep 2026</t>
+  </si>
+  <si>
+    <t>Salary( Expense+</t>
+  </si>
+  <si>
+    <t>Bank Minus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     ( minus 100)</t>
+  </si>
+  <si>
+    <t>( bank or cash account</t>
+  </si>
+  <si>
+    <t>- Account Set up</t>
+  </si>
+  <si>
+    <t>Income/Receive</t>
+  </si>
+  <si>
+    <t>Credit Invoice</t>
+  </si>
+  <si>
+    <t>Vendor/Agent/Carrier Inv No</t>
+  </si>
+  <si>
+    <t>Transfer From :</t>
+  </si>
+  <si>
+    <t>( All bank account )</t>
+  </si>
+  <si>
+    <t>Transfer To</t>
+  </si>
+  <si>
+    <t>Select account</t>
   </si>
 </sst>
 </file>
@@ -4361,7 +4474,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="344">
+  <cellXfs count="348">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
@@ -4926,10 +5039,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4953,6 +5066,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4964,9 +5080,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5010,6 +5123,16 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5161,7 +5284,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp129.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="20" noThreeD="1" sel="0" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5201,7 +5324,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp138.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="20" noThreeD="1" sel="0" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp139.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5217,11 +5340,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp141.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="20" noThreeD="1" sel="0" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp142.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="20" noThreeD="1" sel="0" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp143.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5233,7 +5356,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp145.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="20" noThreeD="1" sel="0" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp146.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5257,7 +5380,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp150.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="20" noThreeD="1" sel="0" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp151.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5273,11 +5396,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp154.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="20" noThreeD="1" sel="0" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp155.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="20" noThreeD="1" sel="0" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp156.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5285,7 +5408,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp157.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="20" noThreeD="1" sel="0" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp158.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5301,7 +5424,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp160.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="20" noThreeD="1" sel="0" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp161.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5313,7 +5436,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp163.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="20" noThreeD="1" sel="0" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp164.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5329,11 +5452,47 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp167.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="20" noThreeD="1" sel="0" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp168.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="20" noThreeD="1" sel="0" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp169.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="20" noThreeD="1" sel="0" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="20" noThreeD="1" sel="0" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp170.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="20" noThreeD="1" sel="0" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp171.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="20" noThreeD="1" sel="0" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp172.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp173.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp174.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropStyle="combo" dx="20" noThreeD="1" sel="0" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp175.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp176.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12991,23 +13150,23 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>12</xdr:col>
+          <xdr:col>9</xdr:col>
           <xdr:colOff>525780</xdr:colOff>
           <xdr:row>1</xdr:row>
           <xdr:rowOff>137160</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>14</xdr:col>
+          <xdr:col>11</xdr:col>
           <xdr:colOff>220980</xdr:colOff>
           <xdr:row>2</xdr:row>
           <xdr:rowOff>152400</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="237569" name="Drop Down 1" hidden="1">
+            <xdr:cNvPr id="236545" name="Drop Down 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s237569"/>
+                  <a14:compatExt spid="_x0000_s236545"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -13051,23 +13210,23 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>9</xdr:col>
+          <xdr:col>14</xdr:col>
           <xdr:colOff>525780</xdr:colOff>
           <xdr:row>1</xdr:row>
           <xdr:rowOff>137160</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>11</xdr:col>
+          <xdr:col>16</xdr:col>
           <xdr:colOff>220980</xdr:colOff>
           <xdr:row>2</xdr:row>
           <xdr:rowOff>152400</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="236545" name="Drop Down 1" hidden="1">
+            <xdr:cNvPr id="237569" name="Drop Down 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s236545"/>
+                  <a14:compatExt spid="_x0000_s237569"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -13681,23 +13840,23 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>15240</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>22860</xdr:rowOff>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>525780</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>137160</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>1211580</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:col>13</xdr:col>
+          <xdr:colOff>220980</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>152400</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="18433" name="Drop Down 1" hidden="1">
+            <xdr:cNvPr id="294913" name="Drop Down 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s18433"/>
+                  <a14:compatExt spid="_x0000_s294913"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -13736,23 +13895,23 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>15240</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>22860</xdr:rowOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>22860</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>152400</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>22860</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:colOff>15240</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>167640</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="18434" name="Drop Down 2" hidden="1">
+            <xdr:cNvPr id="294914" name="Drop Down 2" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s18434"/>
+                  <a14:compatExt spid="_x0000_s294914"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -13787,53 +13946,61 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1021080</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>510540</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="3" name="Straight Arrow Connector 2"/>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="5425440" y="594360"/>
-          <a:ext cx="678180" cy="320040"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>952500</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>670560</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>60960</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="294915" name="Drop Down 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s294915"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
@@ -14115,6 +14282,508 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>525780</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>137160</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>13</xdr:col>
+          <xdr:colOff>220980</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>152400</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="297985" name="Drop Down 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s297985"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>22860</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>152400</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>15240</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>167640</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="297986" name="Drop Down 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s297986"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>952500</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>670560</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>60960</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="297987" name="Drop Down 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s297987"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing41.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>525780</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>137160</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>13</xdr:col>
+          <xdr:colOff>220980</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>152400</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="299009" name="Drop Down 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s299009"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>952500</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>670560</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>60960</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="299011" name="Drop Down 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s299011"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>7620</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>160020</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>167640</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="299012" name="Drop Down 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s299012"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing42.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>15240</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>22860</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>1211580</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="18433" name="Drop Down 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s18433"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>15240</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>22860</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>22860</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="18434" name="Drop Down 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s18434"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1021080</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>510540</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="5425440" y="594360"/>
+          <a:ext cx="678180" cy="320040"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing43.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
           <xdr:col>2</xdr:col>
           <xdr:colOff>22860</xdr:colOff>
           <xdr:row>3</xdr:row>
@@ -14318,7 +14987,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing44.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -14378,7 +15047,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing45.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -14599,7 +15268,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing46.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -14659,7 +15328,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing47.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -14884,7 +15553,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing48.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -15109,7 +15778,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing49.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -15224,7 +15893,342 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>876300</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>22860</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5121" name="Drop Down 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s5121"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>15240</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>891540</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5122" name="Drop Down 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s5122"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>7620</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>883920</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>22860</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5123" name="Drop Down 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s5123"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>10</xdr:col>
+          <xdr:colOff>22860</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>22860</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>10</xdr:col>
+          <xdr:colOff>899160</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5124" name="Drop Down 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s5124"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>22860</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>13</xdr:col>
+          <xdr:colOff>30480</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>15240</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5125" name="Drop Down 5" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s5125"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>7620</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>30480</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>883920</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>22860</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5126" name="Drop Down 6" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s5126"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing50.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -15296,7 +16300,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing51.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -15368,7 +16372,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing52.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -15762,342 +16766,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>876300</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>22860</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5121" name="Drop Down 1" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5121"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>15240</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>891540</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5122" name="Drop Down 2" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5122"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>7620</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>883920</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>22860</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5123" name="Drop Down 3" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5123"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>22860</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>22860</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>899160</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5124" name="Drop Down 4" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5124"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>12</xdr:col>
-          <xdr:colOff>22860</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>13</xdr:col>
-          <xdr:colOff>30480</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5125" name="Drop Down 5" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5125"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>7620</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>883920</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>22860</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5126" name="Drop Down 6" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5126"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing50.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing53.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -16538,7 +17207,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing54.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -16610,7 +17279,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing55.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -17191,7 +17860,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing56.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -17263,7 +17932,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing57.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -17437,7 +18106,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing58.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -17509,7 +18178,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing59.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -19022,7 +19691,7 @@
       </c>
       <c r="L4" s="63"/>
       <c r="M4" s="65" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="N4" s="63"/>
       <c r="O4" s="63"/>
@@ -19062,8 +19731,8 @@
         <v>895</v>
       </c>
       <c r="L5" s="63"/>
-      <c r="M5" s="66" t="s">
-        <v>1153</v>
+      <c r="M5" s="65" t="s">
+        <v>1151</v>
       </c>
       <c r="N5" s="63"/>
       <c r="O5" s="63"/>
@@ -19250,7 +19919,7 @@
       <c r="J11" s="63"/>
       <c r="K11" s="63"/>
       <c r="L11" s="63"/>
-      <c r="M11" s="63" t="s">
+      <c r="M11" s="301" t="s">
         <v>968</v>
       </c>
       <c r="N11" s="63"/>
@@ -19270,7 +19939,7 @@
       <c r="J12" s="63"/>
       <c r="K12" s="63"/>
       <c r="L12" s="63"/>
-      <c r="M12" s="63" t="s">
+      <c r="M12" s="301" t="s">
         <v>969</v>
       </c>
       <c r="N12" s="63"/>
@@ -19346,7 +20015,9 @@
       <c r="J17" s="63"/>
       <c r="K17" s="63"/>
       <c r="L17" s="63"/>
-      <c r="M17" s="66"/>
+      <c r="M17" s="66" t="s">
+        <v>15</v>
+      </c>
       <c r="N17" s="63"/>
       <c r="O17" s="63"/>
     </row>
@@ -19358,7 +20029,9 @@
       <c r="J18" s="63"/>
       <c r="K18" s="63"/>
       <c r="L18" s="63"/>
-      <c r="M18" s="66"/>
+      <c r="M18" s="65" t="s">
+        <v>1170</v>
+      </c>
       <c r="N18" s="63"/>
       <c r="O18" s="63"/>
     </row>
@@ -19370,7 +20043,9 @@
       <c r="J19" s="63"/>
       <c r="K19" s="63"/>
       <c r="L19" s="63"/>
-      <c r="M19" s="66"/>
+      <c r="M19" s="65" t="s">
+        <v>1191</v>
+      </c>
       <c r="N19" s="63"/>
       <c r="O19" s="63"/>
     </row>
@@ -19807,8 +20482,13 @@
     <hyperlink ref="M7" location="'Chart of accounts'!A1" display="-Chat of accounts"/>
     <hyperlink ref="M9" location="Journal!A1" display="      '- Journal"/>
     <hyperlink ref="M10" location="'Expense-regular'!A1" display="      '- Expense"/>
-    <hyperlink ref="M4" location="'Debit note (Other)'!A1" display="- Debit Invoice"/>
+    <hyperlink ref="M4" location="'Debit Invoice'!A1" display="- Debit Invoice"/>
     <hyperlink ref="M3" location="'Awaiting Debit Note'!A1" display="- Awaiting Freight Inv"/>
+    <hyperlink ref="M18" location="'bank setup'!A1" display="; - Bank Set up"/>
+    <hyperlink ref="M19" location="'Account setup'!A1" display="- Account Set up"/>
+    <hyperlink ref="M11" location="'Income-Other'!A1" display="      '- Income"/>
+    <hyperlink ref="M5" location="'Credit Invoice'!A1" display="- Credit Invoice"/>
+    <hyperlink ref="M12" location="'Internal Transfer'!A1" display="       '-Internal Transfer"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -32039,10 +32719,10 @@
       <c r="M2" s="12"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="F3" s="316"/>
-      <c r="G3" s="316"/>
-      <c r="H3" s="316"/>
-      <c r="I3" s="316"/>
+      <c r="F3" s="317"/>
+      <c r="G3" s="317"/>
+      <c r="H3" s="317"/>
+      <c r="I3" s="317"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
@@ -32082,12 +32762,12 @@
       <c r="O5" s="22"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="F7" s="317" t="s">
+      <c r="F7" s="316" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="317"/>
-      <c r="H7" s="317"/>
-      <c r="I7" s="317"/>
+      <c r="G7" s="316"/>
+      <c r="H7" s="316"/>
+      <c r="I7" s="316"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="9" t="s">
@@ -32266,6 +32946,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="J9:J10"/>
     <mergeCell ref="M13:M14"/>
     <mergeCell ref="F7:I7"/>
     <mergeCell ref="B13:B14"/>
@@ -32282,13 +32969,6 @@
     <mergeCell ref="E11:E12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="K11:K12"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="J9:J10"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Menu!A1" display="menu"/>
@@ -32874,10 +33554,10 @@
       <c r="P23" t="s">
         <v>760</v>
       </c>
-      <c r="Q23" s="329" t="s">
+      <c r="Q23" s="325" t="s">
         <v>761</v>
       </c>
-      <c r="R23" s="329"/>
+      <c r="R23" s="325"/>
       <c r="S23" t="s">
         <v>762</v>
       </c>
@@ -33444,13 +34124,13 @@
       <c r="I59" s="239" t="s">
         <v>824</v>
       </c>
-      <c r="J59" s="325" t="s">
+      <c r="J59" s="326" t="s">
         <v>369</v>
       </c>
       <c r="K59" s="237" t="s">
         <v>369</v>
       </c>
-      <c r="L59" s="326" t="s">
+      <c r="L59" s="327" t="s">
         <v>822</v>
       </c>
       <c r="M59" s="322" t="s">
@@ -33481,11 +34161,11 @@
       <c r="I60" s="239" t="s">
         <v>828</v>
       </c>
-      <c r="J60" s="325"/>
+      <c r="J60" s="326"/>
       <c r="K60" s="238" t="s">
         <v>368</v>
       </c>
-      <c r="L60" s="327"/>
+      <c r="L60" s="328"/>
       <c r="M60" s="323"/>
       <c r="N60" s="3" t="s">
         <v>811</v>
@@ -33512,11 +34192,11 @@
       <c r="I61" s="239" t="s">
         <v>829</v>
       </c>
-      <c r="J61" s="325"/>
+      <c r="J61" s="326"/>
       <c r="K61" s="236" t="s">
         <v>814</v>
       </c>
-      <c r="L61" s="328"/>
+      <c r="L61" s="329"/>
       <c r="M61" s="324"/>
       <c r="N61" s="3" t="s">
         <v>817</v>
@@ -33647,20 +34327,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="J46:J47"/>
-    <mergeCell ref="K46:K47"/>
-    <mergeCell ref="S46:S47"/>
-    <mergeCell ref="L46:L47"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="M46:M47"/>
-    <mergeCell ref="H52:H53"/>
-    <mergeCell ref="J52:J53"/>
-    <mergeCell ref="K52:K53"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="J14:N14"/>
-    <mergeCell ref="Q23:R23"/>
     <mergeCell ref="L66:L67"/>
     <mergeCell ref="S52:S53"/>
     <mergeCell ref="G66:G67"/>
@@ -33677,6 +34343,20 @@
     <mergeCell ref="M59:M61"/>
     <mergeCell ref="I66:I67"/>
     <mergeCell ref="G52:G53"/>
+    <mergeCell ref="H52:H53"/>
+    <mergeCell ref="J52:J53"/>
+    <mergeCell ref="K52:K53"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="J14:N14"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="J46:J47"/>
+    <mergeCell ref="K46:K47"/>
+    <mergeCell ref="S46:S47"/>
+    <mergeCell ref="L46:L47"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="M46:M47"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Menu!A1" display="Menu"/>
@@ -38098,7 +38778,7 @@
         <v>977</v>
       </c>
       <c r="K52" s="48" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.3">
@@ -38207,7 +38887,7 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B61" s="309" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="C61" s="56"/>
       <c r="D61" s="56"/>
@@ -38221,7 +38901,7 @@
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B64" s="308" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="C64" s="308" t="s">
         <v>843</v>
@@ -38230,7 +38910,7 @@
         <v>904</v>
       </c>
       <c r="E64" s="308" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
     </row>
   </sheetData>
@@ -38319,508 +38999,12 @@
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="14.5546875" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B3" s="40"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="42"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O5" s="20" t="s">
-        <v>1158</v>
-      </c>
-      <c r="P5" s="34"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="H6" s="32"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>508</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>509</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>566</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>1154</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>398</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="K7" s="140" t="s">
-        <v>1155</v>
-      </c>
-      <c r="L7" s="140" t="s">
-        <v>146</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="N7" s="318" t="s">
-        <v>118</v>
-      </c>
-      <c r="O7" s="319"/>
-      <c r="P7" s="319"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="117" t="s">
-        <v>365</v>
-      </c>
-      <c r="C8" s="118"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="2" t="s">
-        <v>1156</v>
-      </c>
-      <c r="O8" s="124" t="s">
-        <v>434</v>
-      </c>
-      <c r="P8" s="80" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B9" s="117" t="s">
-        <v>366</v>
-      </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="80"/>
-      <c r="P9" s="80"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B10" s="117" t="s">
-        <v>367</v>
-      </c>
-      <c r="C10" s="118"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="80"/>
-      <c r="P10" s="80"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="80"/>
-      <c r="P11" s="80"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="N13" s="2"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B15" s="132" t="s">
-        <v>112</v>
-      </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="34"/>
-      <c r="G15" t="s">
-        <v>1160</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B16" s="132" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="34"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="132" t="s">
-        <v>566</v>
-      </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="34"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="132" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C18" s="43"/>
-      <c r="D18" s="45"/>
-      <c r="F18" s="21"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="148" t="s">
-        <v>92</v>
-      </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="34"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="3" t="s">
-        <v>1155</v>
-      </c>
-      <c r="C20" s="50"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="72" t="s">
-        <v>146</v>
-      </c>
-      <c r="F20" s="72"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="N7:P7"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Menu!A1" display="Menu"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="14.5546875" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
-    <col min="6" max="6" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B3" s="40"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41" t="s">
-        <v>1001</v>
-      </c>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="42"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D7" s="333" t="s">
-        <v>1000</v>
-      </c>
-      <c r="E7" s="333"/>
-      <c r="F7" s="333" t="s">
-        <v>999</v>
-      </c>
-      <c r="G7" s="333"/>
-    </row>
-    <row r="8" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B8" s="296" t="s">
-        <v>148</v>
-      </c>
-      <c r="C8" s="296" t="s">
-        <v>989</v>
-      </c>
-      <c r="D8" s="297" t="s">
-        <v>990</v>
-      </c>
-      <c r="E8" s="297" t="s">
-        <v>991</v>
-      </c>
-      <c r="F8" s="298" t="s">
-        <v>992</v>
-      </c>
-      <c r="G8" s="298" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="3">
-        <v>1</v>
-      </c>
-      <c r="C9" s="109" t="s">
-        <v>994</v>
-      </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="209"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="3">
-        <v>2</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>995</v>
-      </c>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="209"/>
-      <c r="G10" s="209"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="3">
-        <v>3</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>996</v>
-      </c>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="209"/>
-      <c r="G11" s="209"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="3">
-        <v>4</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>997</v>
-      </c>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="209"/>
-      <c r="G12" s="209"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="3">
-        <v>5</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="209"/>
-      <c r="G13" s="209"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="3">
-        <v>6</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="209"/>
-      <c r="G14" s="209"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="3">
-        <v>7</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="209"/>
-      <c r="G15" s="209"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="3">
-        <v>8</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="209"/>
-      <c r="G16" s="209"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="3">
-        <v>9</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="209"/>
-      <c r="G17" s="209"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="209"/>
-      <c r="G18" s="209"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C19" s="73" t="s">
-        <v>998</v>
-      </c>
-      <c r="D19" s="222"/>
-      <c r="E19" s="222"/>
-      <c r="F19" s="222"/>
-      <c r="G19" s="222"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Menu!A1" display="Menu"/>
-    <hyperlink ref="C9" location="Ledger.!A1" display="CMA-CGM"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x14">
-      <controls>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="237569" r:id="rId3" name="Drop Down 1">
-              <controlPr defaultSize="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>12</xdr:col>
-                    <xdr:colOff>525780</xdr:colOff>
-                    <xdr:row>1</xdr:row>
-                    <xdr:rowOff>137160</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>14</xdr:col>
-                    <xdr:colOff>220980</xdr:colOff>
-                    <xdr:row>2</xdr:row>
-                    <xdr:rowOff>152400</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-      </controls>
-    </mc:Choice>
-  </mc:AlternateContent>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.5546875" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="12.44140625" customWidth="1"/>
     <col min="5" max="5" width="14.5546875" customWidth="1"/>
     <col min="6" max="6" width="19.88671875" bestFit="1" customWidth="1"/>
@@ -38845,31 +39029,31 @@
       <c r="E3" s="41"/>
       <c r="F3" s="41"/>
       <c r="G3" s="41" t="s">
-        <v>1002</v>
+        <v>1193</v>
       </c>
       <c r="H3" s="307"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="100" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>1003</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>1005</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>516</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="I7" s="334" t="s">
         <v>118</v>
@@ -38882,10 +39066,10 @@
         <v>46275</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="E8" s="3">
         <v>2000</v>
@@ -38898,10 +39082,10 @@
         <v>248000</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="I8" s="109" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>56</v>
@@ -39019,6 +39203,485 @@
                   </from>
                   <to>
                     <xdr:col>11</xdr:col>
+                    <xdr:colOff>220980</xdr:colOff>
+                    <xdr:row>2</xdr:row>
+                    <xdr:rowOff>152400</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B3" s="40"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="42"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O5" s="20" t="s">
+        <v>1156</v>
+      </c>
+      <c r="P5" s="34"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="H6" s="32"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="K7" s="140" t="s">
+        <v>1153</v>
+      </c>
+      <c r="L7" s="140" t="s">
+        <v>146</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="N7" s="318" t="s">
+        <v>118</v>
+      </c>
+      <c r="O7" s="319"/>
+      <c r="P7" s="319"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B8" s="117" t="s">
+        <v>365</v>
+      </c>
+      <c r="C8" s="118"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="O8" s="124" t="s">
+        <v>434</v>
+      </c>
+      <c r="P8" s="80" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B9" s="117" t="s">
+        <v>366</v>
+      </c>
+      <c r="C9" s="118"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="80"/>
+      <c r="P9" s="80"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B10" s="117" t="s">
+        <v>367</v>
+      </c>
+      <c r="C10" s="118"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="80"/>
+      <c r="P10" s="80"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="80"/>
+      <c r="P11" s="80"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N13" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="N7:P7"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Menu!A1" display="Menu"/>
+    <hyperlink ref="N8" location="Income!A1" display="Receive"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="7" width="14.5546875" customWidth="1"/>
+    <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23" customWidth="1"/>
+    <col min="10" max="10" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B3" s="40"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41" t="s">
+        <v>1001</v>
+      </c>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="42"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D7" s="333" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E7" s="333"/>
+      <c r="F7" s="344" t="s">
+        <v>1164</v>
+      </c>
+      <c r="G7" s="345"/>
+      <c r="H7" s="333" t="s">
+        <v>999</v>
+      </c>
+      <c r="I7" s="333"/>
+    </row>
+    <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B8" s="296" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="296" t="s">
+        <v>989</v>
+      </c>
+      <c r="D8" s="297" t="s">
+        <v>990</v>
+      </c>
+      <c r="E8" s="297" t="s">
+        <v>991</v>
+      </c>
+      <c r="F8" s="346" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G8" s="346" t="s">
+        <v>1166</v>
+      </c>
+      <c r="H8" s="298" t="s">
+        <v>992</v>
+      </c>
+      <c r="I8" s="298" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>994</v>
+      </c>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="281"/>
+      <c r="G9" s="281"/>
+      <c r="H9" s="209"/>
+      <c r="I9" s="209"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B10" s="3">
+        <v>2</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="281"/>
+      <c r="G10" s="281"/>
+      <c r="H10" s="209"/>
+      <c r="I10" s="209"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B11" s="3">
+        <v>3</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="281"/>
+      <c r="G11" s="281"/>
+      <c r="H11" s="209"/>
+      <c r="I11" s="209"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B12" s="3">
+        <v>4</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="281"/>
+      <c r="G12" s="281"/>
+      <c r="H12" s="209"/>
+      <c r="I12" s="209"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B13" s="3">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="281"/>
+      <c r="G13" s="281"/>
+      <c r="H13" s="209"/>
+      <c r="I13" s="209"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B14" s="3">
+        <v>6</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="281"/>
+      <c r="G14" s="281"/>
+      <c r="H14" s="209"/>
+      <c r="I14" s="209"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B15" s="3">
+        <v>7</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="281"/>
+      <c r="G15" s="281"/>
+      <c r="H15" s="209"/>
+      <c r="I15" s="209"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B16" s="3">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="281"/>
+      <c r="G16" s="281"/>
+      <c r="H16" s="209"/>
+      <c r="I16" s="209"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B17" s="3">
+        <v>9</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="281"/>
+      <c r="G17" s="281"/>
+      <c r="H17" s="209"/>
+      <c r="I17" s="209"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="281"/>
+      <c r="G18" s="281"/>
+      <c r="H18" s="209"/>
+      <c r="I18" s="209"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="73" t="s">
+        <v>998</v>
+      </c>
+      <c r="D19" s="222"/>
+      <c r="E19" s="222"/>
+      <c r="F19" s="222"/>
+      <c r="G19" s="222"/>
+      <c r="H19" s="222"/>
+      <c r="I19" s="222"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="F7:G7"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Menu!A1" display="Menu"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="237569" r:id="rId3" name="Drop Down 1">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>14</xdr:col>
+                    <xdr:colOff>525780</xdr:colOff>
+                    <xdr:row>1</xdr:row>
+                    <xdr:rowOff>137160</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>16</xdr:col>
                     <xdr:colOff>220980</xdr:colOff>
                     <xdr:row>2</xdr:row>
                     <xdr:rowOff>152400</xdr:rowOff>
@@ -39354,7 +40017,7 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD58"/>
+  <dimension ref="A1:AD68"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.5546875" customWidth="1"/>
@@ -39396,7 +40059,7 @@
       <c r="E3" s="41"/>
       <c r="F3" s="41"/>
       <c r="G3" s="41" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="H3" s="41"/>
       <c r="I3" s="41"/>
@@ -39405,401 +40068,404 @@
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B6" s="39" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C6" s="185" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D6" s="284" t="s">
         <v>1008</v>
       </c>
-      <c r="C6" s="185" t="s">
+      <c r="E6" s="299" t="s">
         <v>1009</v>
       </c>
-      <c r="D6" s="284" t="s">
+      <c r="F6" s="185" t="s">
         <v>1010</v>
       </c>
-      <c r="E6" s="299" t="s">
-        <v>1011</v>
-      </c>
-      <c r="F6" s="185" t="s">
-        <v>1012</v>
+      <c r="H6" t="s">
+        <v>1167</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B9" s="39" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C9" s="289" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H9" s="185" t="s">
+        <v>1007</v>
+      </c>
+      <c r="N9" s="284" t="s">
         <v>1008</v>
       </c>
-      <c r="C9" s="289" t="s">
-        <v>1013</v>
-      </c>
-      <c r="H9" s="185" t="s">
+      <c r="T9" s="299" t="s">
         <v>1009</v>
       </c>
-      <c r="N9" s="284" t="s">
+      <c r="Z9" s="185" t="s">
         <v>1010</v>
-      </c>
-      <c r="T9" s="299" t="s">
-        <v>1011</v>
-      </c>
-      <c r="Z9" s="185" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B10" s="63" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C10" s="63"/>
       <c r="D10" s="63"/>
       <c r="E10" s="63"/>
       <c r="F10" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="H10" s="63" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="I10" s="63"/>
       <c r="J10" s="63"/>
       <c r="K10" s="63"/>
       <c r="L10" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="N10" s="63" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="O10" s="63"/>
       <c r="P10" s="63"/>
       <c r="Q10" s="63"/>
       <c r="R10" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="T10" s="63" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="U10" s="63"/>
       <c r="V10" s="63"/>
       <c r="W10" s="63"/>
       <c r="X10" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="Z10" s="63" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="AA10" s="63"/>
       <c r="AB10" s="63"/>
       <c r="AC10" s="63"/>
       <c r="AD10" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="H11" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="N11" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="T11" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="Z11" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="H12" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="N12" s="300" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="Z12" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="H13" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="Z13" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="H14" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="H15" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="H16" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="17" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="H17" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="18" spans="2:30" x14ac:dyDescent="0.3">
       <c r="H18" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="19" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B19" s="63" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C19" s="63"/>
       <c r="D19" s="63"/>
       <c r="E19" s="63"/>
       <c r="F19" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="H19" s="63" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="I19" s="63"/>
       <c r="J19" s="63"/>
       <c r="K19" s="63"/>
       <c r="L19" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="N19" s="63" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="O19" s="63"/>
       <c r="P19" s="63"/>
       <c r="Q19" s="63"/>
       <c r="R19" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="T19" s="63" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="U19" s="63"/>
       <c r="V19" s="63"/>
       <c r="W19" s="63"/>
       <c r="X19" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="Z19" s="63" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="AA19" s="63"/>
       <c r="AB19" s="63"/>
       <c r="AC19" s="63"/>
       <c r="AD19" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="20" spans="2:30" x14ac:dyDescent="0.3">
       <c r="N20" s="300" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="T20" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="Z20" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="21" spans="2:30" x14ac:dyDescent="0.3">
       <c r="T21" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="22" spans="2:30" x14ac:dyDescent="0.3">
       <c r="T22" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="23" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B23" s="63" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C23" s="63"/>
       <c r="D23" s="63"/>
       <c r="E23" s="63"/>
       <c r="F23" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="H23" s="63" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="I23" s="63"/>
       <c r="J23" s="63"/>
       <c r="K23" s="63"/>
       <c r="L23" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="T23" s="63" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="U23" s="63"/>
       <c r="V23" s="63"/>
       <c r="W23" s="63"/>
       <c r="X23" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="Z23" s="63" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="AA23" s="63"/>
       <c r="AB23" s="63"/>
       <c r="AC23" s="63"/>
       <c r="AD23" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="24" spans="2:30" x14ac:dyDescent="0.3">
       <c r="H24" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="T24" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="Z24" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="25" spans="2:30" x14ac:dyDescent="0.3">
       <c r="Z25" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="26" spans="2:30" x14ac:dyDescent="0.3">
       <c r="Z26" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="27" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B27" s="63" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="C27" s="63"/>
       <c r="D27" s="63"/>
       <c r="E27" s="63"/>
       <c r="F27" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="H27" s="63" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="I27" s="63"/>
       <c r="J27" s="63"/>
       <c r="K27" s="63"/>
       <c r="L27" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="T27" s="63" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="U27" s="63"/>
       <c r="V27" s="63"/>
       <c r="W27" s="63"/>
       <c r="X27" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="Z27" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="28" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="Z28" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="29" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Z29" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="30" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="T30" s="63" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="U30" s="63"/>
       <c r="V30" s="63"/>
       <c r="W30" s="63"/>
       <c r="X30" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="Z30" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="31" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="Z31" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="32" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="33" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="T33" s="63" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="U33" s="63"/>
       <c r="V33" s="63"/>
       <c r="W33" s="63"/>
       <c r="X33" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="Z33" s="63" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="AA33" s="63"/>
       <c r="AB33" s="63"/>
       <c r="AC33" s="63"/>
       <c r="AD33" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="34" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="Z34" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="35" spans="2:30" x14ac:dyDescent="0.3">
@@ -39809,168 +40475,189 @@
     </row>
     <row r="36" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="T36" s="63" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="U36" s="63"/>
       <c r="V36" s="63"/>
       <c r="W36" s="63"/>
       <c r="X36" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="Z36" s="63" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="AA36" s="63"/>
       <c r="AB36" s="63"/>
       <c r="AC36" s="63"/>
       <c r="AD36" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="37" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="T37" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="Z37" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="38" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="39" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="Z39" s="63" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="AA39" s="63"/>
       <c r="AB39" s="63"/>
       <c r="AC39" s="63"/>
       <c r="AD39" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="40" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="Z40" s="300" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="41" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="Z41" s="300" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="42" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="Z42" s="63" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="AA42" s="63"/>
       <c r="AB42" s="63"/>
       <c r="AC42" s="63"/>
       <c r="AD42" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="43" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="Z43" s="300"/>
     </row>
     <row r="44" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="45" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="46" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="47" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="48" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="63" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C53" s="63"/>
       <c r="D53" s="63"/>
       <c r="E53" s="63"/>
       <c r="F53" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" s="63" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C57" s="63"/>
       <c r="D57" s="63"/>
       <c r="E57" s="63"/>
       <c r="F57" s="66" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
-        <v>1045</v>
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B66" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1044</v>
       </c>
     </row>
   </sheetData>
@@ -40047,7 +40734,7 @@
       <c r="E3" s="41"/>
       <c r="F3" s="41"/>
       <c r="G3" s="41" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="H3" s="41"/>
       <c r="I3" s="41"/>
@@ -40055,24 +40742,26 @@
       <c r="K3" s="42"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="281" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C9" s="277" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D9" s="278"/>
+      <c r="E9" s="279"/>
+      <c r="F9" s="277" t="s">
         <v>1093</v>
       </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C9" s="20" t="s">
-        <v>1094</v>
-      </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="20" t="s">
-        <v>1095</v>
-      </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="279"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C10" s="43"/>
+      <c r="C10" s="43" t="s">
+        <v>1186</v>
+      </c>
       <c r="D10" s="44"/>
       <c r="E10" s="45"/>
       <c r="F10" s="43"/>
@@ -40090,7 +40779,7 @@
       <c r="D12" s="21"/>
       <c r="E12" s="48"/>
       <c r="F12" s="46" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="G12" s="48"/>
     </row>
@@ -40122,51 +40811,61 @@
       <c r="F16" s="50"/>
       <c r="G16" s="51"/>
     </row>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C19" s="20" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C19" s="277" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D19" s="278"/>
+      <c r="E19" s="279"/>
+      <c r="F19" s="281" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G19" s="281" t="s">
         <v>1097</v>
       </c>
-      <c r="D19" s="33"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="3" t="s">
-        <v>1098</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="20" spans="3:7" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="2:7" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>1188</v>
+      </c>
       <c r="C20" s="20"/>
       <c r="D20" s="33"/>
       <c r="E20" s="34"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="3:7" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G20" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>1187</v>
+      </c>
       <c r="C21" s="20"/>
       <c r="D21" s="33"/>
       <c r="E21" s="34"/>
-      <c r="F21" s="3"/>
+      <c r="F21" s="3">
+        <v>500000</v>
+      </c>
       <c r="G21" s="3"/>
     </row>
-    <row r="24" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="F24" s="32" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="G24" s="3"/>
     </row>
-    <row r="25" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="F25" s="32" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="G25" s="3"/>
     </row>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="F29" t="s">
         <v>106</v>
       </c>
       <c r="G29" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
   </sheetData>
@@ -40285,7 +40984,7 @@
       <c r="E3" s="41"/>
       <c r="F3" s="41"/>
       <c r="G3" s="41" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="H3" s="41"/>
       <c r="I3" s="41"/>
@@ -40293,51 +40992,51 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C7" s="132" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="D7" s="3"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C9" s="32" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>382</v>
       </c>
       <c r="E9" s="34"/>
       <c r="F9" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="E11" s="34"/>
       <c r="F11" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="K12" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C13" s="32" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="D13" s="43"/>
       <c r="E13" s="44"/>
       <c r="F13" s="45"/>
       <c r="G13" s="3" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="K13" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -40354,25 +41053,28 @@
     </row>
     <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="K16" s="304" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="17" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C17" s="32" t="s">
+        <v>1108</v>
+      </c>
+      <c r="F17" t="s">
         <v>1110</v>
       </c>
-      <c r="F17" t="s">
-        <v>1112</v>
+      <c r="G17" t="s">
+        <v>1189</v>
       </c>
     </row>
     <row r="18" spans="3:11" x14ac:dyDescent="0.3">
       <c r="K18" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="19" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C19" s="12" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="12"/>
@@ -40381,57 +41083,59 @@
     </row>
     <row r="20" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
+        <v>1112</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K20" s="211" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="21" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="G21" s="3">
+        <v>100</v>
+      </c>
+      <c r="H21" s="303" t="s">
         <v>1114</v>
-      </c>
-      <c r="G20" t="s">
-        <v>1115</v>
-      </c>
-      <c r="K20" s="211" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="G21" s="3"/>
-      <c r="H21" s="303" t="s">
-        <v>1116</v>
       </c>
       <c r="K21" s="305"/>
     </row>
     <row r="22" spans="3:11" x14ac:dyDescent="0.3">
       <c r="K22" s="306" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="23" spans="3:11" x14ac:dyDescent="0.3">
       <c r="K23" s="306" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="24" spans="3:11" x14ac:dyDescent="0.3">
       <c r="G24" s="132" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="3:11" x14ac:dyDescent="0.3">
       <c r="G25" s="132" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="H25" s="3"/>
       <c r="K25" s="211" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="26" spans="3:11" x14ac:dyDescent="0.3">
       <c r="G26" s="132" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="H26" s="3"/>
       <c r="K26" s="305"/>
     </row>
     <row r="27" spans="3:11" x14ac:dyDescent="0.3">
       <c r="K27" s="305" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="28" spans="3:11" x14ac:dyDescent="0.3">
@@ -40439,40 +41143,40 @@
         <v>106</v>
       </c>
       <c r="K28" s="305" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="30" spans="3:11" ht="18" x14ac:dyDescent="0.3">
       <c r="K30" s="304" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="32" spans="3:11" x14ac:dyDescent="0.3">
       <c r="K32" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="34" spans="3:11" ht="18" x14ac:dyDescent="0.3">
       <c r="C34" s="304" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="K34" s="211" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="35" spans="3:11" x14ac:dyDescent="0.3">
       <c r="K35" s="211" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="36" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="38" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C38" s="211" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="39" spans="3:11" x14ac:dyDescent="0.3">
@@ -40480,27 +41184,27 @@
     </row>
     <row r="40" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C40" s="306" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="41" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C41" s="306" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="43" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C43" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="45" spans="3:11" ht="18" x14ac:dyDescent="0.3">
       <c r="C45" s="304" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="47" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C47" s="211" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="48" spans="3:11" x14ac:dyDescent="0.3">
@@ -40508,17 +41212,17 @@
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C49" s="305" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="50" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C50" s="305" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="52" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C52" s="211" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="53" spans="3:3" x14ac:dyDescent="0.3">
@@ -40526,12 +41230,12 @@
     </row>
     <row r="54" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C54" s="305" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="55" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C55" s="305" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
     </row>
   </sheetData>
@@ -40650,7 +41354,7 @@
       <c r="E3" s="41"/>
       <c r="F3" s="41"/>
       <c r="G3" s="41" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="H3" s="41"/>
       <c r="I3" s="41"/>
@@ -40658,27 +41362,27 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C7" s="132" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="D7" s="3"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="K9" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C10" s="32" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="D10" s="43"/>
       <c r="E10" s="44"/>
       <c r="F10" s="45"/>
       <c r="G10" s="3" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="K10" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -40695,25 +41399,25 @@
     </row>
     <row r="13" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="K13" s="304" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C14" s="32" t="s">
+        <v>1108</v>
+      </c>
+      <c r="F14" t="s">
         <v>1110</v>
-      </c>
-      <c r="F14" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="K15" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C16" s="12" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
@@ -40722,57 +41426,57 @@
     </row>
     <row r="17" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="G17" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="K17" s="211" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="18" spans="3:11" x14ac:dyDescent="0.3">
       <c r="G18" s="3"/>
       <c r="H18" s="303" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="K18" s="305"/>
     </row>
     <row r="19" spans="3:11" x14ac:dyDescent="0.3">
       <c r="K19" s="306" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="20" spans="3:11" x14ac:dyDescent="0.3">
       <c r="K20" s="306" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="21" spans="3:11" x14ac:dyDescent="0.3">
       <c r="G21" s="132" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H21" s="3"/>
     </row>
     <row r="22" spans="3:11" x14ac:dyDescent="0.3">
       <c r="G22" s="132" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="H22" s="3"/>
       <c r="K22" s="211" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="23" spans="3:11" x14ac:dyDescent="0.3">
       <c r="G23" s="132" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="H23" s="3"/>
       <c r="K23" s="305"/>
     </row>
     <row r="24" spans="3:11" x14ac:dyDescent="0.3">
       <c r="K24" s="305" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="25" spans="3:11" x14ac:dyDescent="0.3">
@@ -40780,28 +41484,28 @@
         <v>106</v>
       </c>
       <c r="K25" s="305" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="27" spans="3:11" ht="18" x14ac:dyDescent="0.3">
       <c r="K27" s="304" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="29" spans="3:11" x14ac:dyDescent="0.3">
       <c r="K29" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="31" spans="3:11" ht="18" x14ac:dyDescent="0.3">
       <c r="C31" s="304"/>
       <c r="K31" s="211" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="32" spans="3:11" x14ac:dyDescent="0.3">
       <c r="K32" s="211" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="35" spans="3:3" x14ac:dyDescent="0.3">
@@ -40927,6 +41631,827 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="6" max="6" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B3" s="40"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="42"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C7" s="132" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C9" s="32" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D9" s="20"/>
+      <c r="E9" s="34"/>
+      <c r="F9" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D11" s="20"/>
+      <c r="E11" s="34"/>
+      <c r="F11" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C13" s="32" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D13" s="43"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D14" s="46"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="71"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D15" s="50"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="72"/>
+    </row>
+    <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.3">
+      <c r="K16" s="304"/>
+    </row>
+    <row r="17" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C17" s="32" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="19" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C19" s="12" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="302"/>
+    </row>
+    <row r="20" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K20" s="211"/>
+    </row>
+    <row r="21" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="G21" s="3"/>
+      <c r="H21" s="303" t="s">
+        <v>1114</v>
+      </c>
+      <c r="K21" s="305"/>
+    </row>
+    <row r="22" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="K22" s="306"/>
+    </row>
+    <row r="23" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="K23" s="306"/>
+    </row>
+    <row r="24" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="G24" s="132" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="G25" s="132" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H25" s="3"/>
+      <c r="K25" s="211"/>
+    </row>
+    <row r="26" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="G26" s="132" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H26" s="3"/>
+      <c r="K26" s="305"/>
+    </row>
+    <row r="27" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="K27" s="305"/>
+    </row>
+    <row r="28" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="H28" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K28" s="305"/>
+    </row>
+    <row r="30" spans="3:11" ht="18" x14ac:dyDescent="0.3">
+      <c r="K30" s="304"/>
+    </row>
+    <row r="34" spans="3:11" ht="18" x14ac:dyDescent="0.3">
+      <c r="C34" s="304"/>
+      <c r="K34" s="211"/>
+    </row>
+    <row r="35" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="K35" s="211"/>
+    </row>
+    <row r="38" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C38" s="211"/>
+    </row>
+    <row r="39" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C39" s="305"/>
+    </row>
+    <row r="40" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C40" s="306"/>
+    </row>
+    <row r="41" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C41" s="306"/>
+    </row>
+    <row r="45" spans="3:11" ht="18" x14ac:dyDescent="0.3">
+      <c r="C45" s="304"/>
+    </row>
+    <row r="47" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C47" s="211"/>
+    </row>
+    <row r="48" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C48" s="305"/>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C49" s="305"/>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C50" s="305"/>
+    </row>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C52" s="211"/>
+    </row>
+    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C53" s="305"/>
+    </row>
+    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C54" s="305"/>
+    </row>
+    <row r="55" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C55" s="305"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Menu!A1" display="Menu"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="294913" r:id="rId3" name="Drop Down 1">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>11</xdr:col>
+                    <xdr:colOff>525780</xdr:colOff>
+                    <xdr:row>1</xdr:row>
+                    <xdr:rowOff>137160</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>13</xdr:col>
+                    <xdr:colOff>220980</xdr:colOff>
+                    <xdr:row>2</xdr:row>
+                    <xdr:rowOff>152400</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="294914" r:id="rId4" name="Drop Down 2">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>22860</xdr:colOff>
+                    <xdr:row>15</xdr:row>
+                    <xdr:rowOff>152400</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>15240</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>167640</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="294915" r:id="rId5" name="Drop Down 3">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>952500</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>670560</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>60960</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K52"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="6" max="6" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B3" s="40"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="42"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C7" s="132" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C10" s="32" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D11" s="46"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="71"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D12" s="50"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="72"/>
+    </row>
+    <row r="13" spans="1:11" ht="18" x14ac:dyDescent="0.3">
+      <c r="K13" s="304"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C14" s="32" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C16" s="12" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="302"/>
+    </row>
+    <row r="17" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K17" s="211"/>
+    </row>
+    <row r="18" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="G18" s="3"/>
+      <c r="H18" s="303" t="s">
+        <v>1114</v>
+      </c>
+      <c r="K18" s="305"/>
+    </row>
+    <row r="19" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="K19" s="306"/>
+    </row>
+    <row r="20" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="K20" s="306"/>
+    </row>
+    <row r="21" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="G21" s="132" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="G22" s="132" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="K22" s="211"/>
+    </row>
+    <row r="23" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="G23" s="132" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H23" s="3"/>
+      <c r="K23" s="305"/>
+    </row>
+    <row r="24" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="K24" s="305"/>
+    </row>
+    <row r="25" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="H25" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K25" s="305"/>
+    </row>
+    <row r="27" spans="3:11" ht="18" x14ac:dyDescent="0.3">
+      <c r="K27" s="304"/>
+    </row>
+    <row r="31" spans="3:11" ht="18" x14ac:dyDescent="0.3">
+      <c r="C31" s="304"/>
+      <c r="K31" s="211"/>
+    </row>
+    <row r="32" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="K32" s="211"/>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C35" s="211"/>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C36" s="305"/>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C37" s="306"/>
+    </row>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C38" s="306"/>
+    </row>
+    <row r="42" spans="3:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="C42" s="304"/>
+    </row>
+    <row r="44" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C44" s="211"/>
+    </row>
+    <row r="45" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C45" s="305"/>
+    </row>
+    <row r="46" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C46" s="305"/>
+    </row>
+    <row r="47" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C47" s="305"/>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C49" s="211"/>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C50" s="305"/>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C51" s="305"/>
+    </row>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C52" s="305"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Menu!A1" display="Menu"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="297985" r:id="rId3" name="Drop Down 1">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>11</xdr:col>
+                    <xdr:colOff>525780</xdr:colOff>
+                    <xdr:row>1</xdr:row>
+                    <xdr:rowOff>137160</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>13</xdr:col>
+                    <xdr:colOff>220980</xdr:colOff>
+                    <xdr:row>2</xdr:row>
+                    <xdr:rowOff>152400</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="297986" r:id="rId4" name="Drop Down 2">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>22860</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>152400</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>15240</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>167640</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="297987" r:id="rId5" name="Drop Down 3">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>952500</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>670560</xdr:colOff>
+                    <xdr:row>18</xdr:row>
+                    <xdr:rowOff>60960</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="6" max="6" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B3" s="40"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="42"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C7" s="132" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C9" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C11" s="32" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D11" s="43"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D12" s="46"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="71"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D13" s="50"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="72"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C15" s="12" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="302"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>1198</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K16" s="211"/>
+    </row>
+    <row r="17" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="G17" s="3"/>
+      <c r="H17" s="303" t="s">
+        <v>1114</v>
+      </c>
+      <c r="K17" s="305"/>
+    </row>
+    <row r="18" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="K18" s="306"/>
+    </row>
+    <row r="19" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="K19" s="306"/>
+    </row>
+    <row r="20" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="G20" s="132" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="G21" s="132" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H21" s="3"/>
+      <c r="K21" s="211"/>
+    </row>
+    <row r="22" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="G22" s="132" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="K22" s="305"/>
+    </row>
+    <row r="23" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="K23" s="305"/>
+    </row>
+    <row r="24" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="H24" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K24" s="305"/>
+    </row>
+    <row r="26" spans="3:11" ht="18" x14ac:dyDescent="0.3">
+      <c r="K26" s="304"/>
+    </row>
+    <row r="30" spans="3:11" ht="18" x14ac:dyDescent="0.3">
+      <c r="C30" s="304"/>
+      <c r="K30" s="211"/>
+    </row>
+    <row r="31" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="K31" s="211"/>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C34" s="211"/>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C35" s="305"/>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C36" s="306"/>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C37" s="306"/>
+    </row>
+    <row r="41" spans="3:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="C41" s="304"/>
+    </row>
+    <row r="43" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C43" s="211"/>
+    </row>
+    <row r="44" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C44" s="305"/>
+    </row>
+    <row r="45" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C45" s="305"/>
+    </row>
+    <row r="46" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C46" s="305"/>
+    </row>
+    <row r="48" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C48" s="211"/>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C49" s="305"/>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C50" s="305"/>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C51" s="305"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Menu!A1" display="Menu"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="299009" r:id="rId3" name="Drop Down 1">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>11</xdr:col>
+                    <xdr:colOff>525780</xdr:colOff>
+                    <xdr:row>1</xdr:row>
+                    <xdr:rowOff>137160</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>13</xdr:col>
+                    <xdr:colOff>220980</xdr:colOff>
+                    <xdr:row>2</xdr:row>
+                    <xdr:rowOff>152400</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="299011" r:id="rId4" name="Drop Down 3">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>952500</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>670560</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>60960</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="299012" r:id="rId5" name="Drop Down 4">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>7620</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>160020</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>167640</xdr:colOff>
+                    <xdr:row>9</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -41233,7 +42758,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -41499,7 +43024,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -41624,708 +43149,6 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.21875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="F6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="81" t="s">
-        <v>152</v>
-      </c>
-      <c r="D9" s="81" t="s">
-        <v>151</v>
-      </c>
-      <c r="E9" s="81" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="81" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="I10" s="73" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="I11" s="38" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="I12" s="71" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="I13" s="72" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Menu!A1" display="menu"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x14">
-      <controls>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="23553" r:id="rId3" name="Drop Down 1">
-              <controlPr defaultSize="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>30480</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>15240</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>1066800</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>7620</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-      </controls>
-    </mc:Choice>
-  </mc:AlternateContent>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.77734375" customWidth="1"/>
-    <col min="6" max="6" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="12" max="12" width="19.77734375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G4" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C5" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C6" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G8" s="108" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="106"/>
-      <c r="I8" s="107"/>
-      <c r="J8" s="114"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C9" s="81" t="s">
-        <v>152</v>
-      </c>
-      <c r="D9" s="81" t="s">
-        <v>159</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="F9" s="81" t="s">
-        <v>161</v>
-      </c>
-      <c r="G9" s="335" t="s">
-        <v>149</v>
-      </c>
-      <c r="H9" s="336"/>
-      <c r="I9" s="336"/>
-      <c r="J9" s="115"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C10" s="3"/>
-      <c r="D10" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="H10" s="109" t="s">
-        <v>342</v>
-      </c>
-      <c r="I10" s="109" t="s">
-        <v>343</v>
-      </c>
-      <c r="J10" s="116" t="s">
-        <v>361</v>
-      </c>
-      <c r="L10" s="73" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C11" s="3"/>
-      <c r="D11" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="21"/>
-      <c r="L11" s="71" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C12" s="3"/>
-      <c r="D12" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="21"/>
-      <c r="L12" s="71" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="21"/>
-      <c r="L13" s="71" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="21"/>
-      <c r="L14" s="71" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="21"/>
-      <c r="L15" s="72"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="21"/>
-    </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E19" t="s">
-        <v>447</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="G9:I9"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Menu!A1" display="menu"/>
-    <hyperlink ref="H10" location="Carrier_PIC!A1" display="ADD PIC "/>
-    <hyperlink ref="I10" location="'Carrier Service Port'!A1" display="Service Port"/>
-    <hyperlink ref="J10" location="'Carrier Service Port_pair'!A1" display="Port Pair"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x14">
-      <controls>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="24578" r:id="rId4" name="Drop Down 2">
-              <controlPr defaultSize="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>22860</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>1196340</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>175260</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="24579" r:id="rId5" name="Button 3">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!ADD">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>182880</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>160020</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>701040</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>15240</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-      </controls>
-    </mc:Choice>
-  </mc:AlternateContent>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="5" width="15.109375" customWidth="1"/>
-    <col min="6" max="6" width="15.77734375" customWidth="1"/>
-    <col min="7" max="7" width="16.77734375" customWidth="1"/>
-    <col min="8" max="8" width="15.88671875" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.77734375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C4" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="K5" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="I7" s="84" t="s">
-        <v>123</v>
-      </c>
-      <c r="J7" s="34"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B8" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="M9" s="71" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="M10" s="71" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="M11" s="71" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="M12" s="71" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="M13" s="71" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="M14" s="71" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="M15" s="71" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="M16" s="71" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="M17" s="72" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="J24" s="85" t="s">
-        <v>176</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Menu!A1" display="Menu"/>
-    <hyperlink ref="J24" location="Carrier!A1" display="Back to list"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x14">
-      <controls>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="26625" r:id="rId3" name="Drop Down 1">
-              <controlPr defaultSize="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>8</xdr:col>
-                    <xdr:colOff>7620</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>22860</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>8</xdr:col>
-                    <xdr:colOff>762000</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-      </controls>
-    </mc:Choice>
-  </mc:AlternateContent>
 </worksheet>
 </file>
 
@@ -42706,6 +43529,708 @@
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C5" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="F6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="81" t="s">
+        <v>152</v>
+      </c>
+      <c r="D9" s="81" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9" s="81" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="81" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="I10" s="73" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="I11" s="38" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="I12" s="71" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="I13" s="72" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Menu!A1" display="menu"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="23553" r:id="rId3" name="Drop Down 1">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>30480</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>15240</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>1066800</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>7620</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.77734375" customWidth="1"/>
+    <col min="6" max="6" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="12" max="12" width="19.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G4" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C6" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G8" s="108" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="106"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="114"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C9" s="81" t="s">
+        <v>152</v>
+      </c>
+      <c r="D9" s="81" t="s">
+        <v>159</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F9" s="81" t="s">
+        <v>161</v>
+      </c>
+      <c r="G9" s="335" t="s">
+        <v>149</v>
+      </c>
+      <c r="H9" s="336"/>
+      <c r="I9" s="336"/>
+      <c r="J9" s="115"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="H10" s="109" t="s">
+        <v>342</v>
+      </c>
+      <c r="I10" s="109" t="s">
+        <v>343</v>
+      </c>
+      <c r="J10" s="116" t="s">
+        <v>361</v>
+      </c>
+      <c r="L10" s="73" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="21"/>
+      <c r="L11" s="71" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="21"/>
+      <c r="L12" s="71" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="21"/>
+      <c r="L13" s="71" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="21"/>
+      <c r="L14" s="71" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="21"/>
+      <c r="L15" s="72"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="21"/>
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
+        <v>447</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G9:I9"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Menu!A1" display="menu"/>
+    <hyperlink ref="H10" location="Carrier_PIC!A1" display="ADD PIC "/>
+    <hyperlink ref="I10" location="'Carrier Service Port'!A1" display="Service Port"/>
+    <hyperlink ref="J10" location="'Carrier Service Port_pair'!A1" display="Port Pair"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="24578" r:id="rId4" name="Drop Down 2">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>22860</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>1196340</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>175260</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="24579" r:id="rId5" name="Button 3">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!ADD">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>182880</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>160020</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>701040</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>15240</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="5" width="15.109375" customWidth="1"/>
+    <col min="6" max="6" width="15.77734375" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C4" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="K5" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I7" s="84" t="s">
+        <v>123</v>
+      </c>
+      <c r="J7" s="34"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="M9" s="71" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="M10" s="71" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="M11" s="71" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="M12" s="71" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="M13" s="71" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="M14" s="71" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="M15" s="71" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="M16" s="71" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="M17" s="72" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="J24" s="85" t="s">
+        <v>176</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Menu!A1" display="Menu"/>
+    <hyperlink ref="J24" location="Carrier!A1" display="Back to list"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="26625" r:id="rId3" name="Drop Down 1">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>7620</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>762000</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -43124,7 +44649,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -43590,7 +45115,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -43993,7 +45518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -44218,7 +45743,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -44448,7 +45973,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -44661,7 +46186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -45064,7 +46589,399 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+    <col min="4" max="5" width="13.33203125" customWidth="1"/>
+    <col min="10" max="10" width="37.77734375" customWidth="1"/>
+    <col min="11" max="12" width="13.21875" customWidth="1"/>
+    <col min="13" max="13" width="23.6640625" customWidth="1"/>
+    <col min="14" max="14" width="2.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F3" s="317"/>
+      <c r="G3" s="317"/>
+      <c r="H3" s="317"/>
+      <c r="I3" s="317"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="14"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F5" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F7" s="313" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="313"/>
+      <c r="H7" s="313"/>
+      <c r="I7" s="313"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B9" s="314"/>
+      <c r="C9" s="314"/>
+      <c r="D9" s="314"/>
+      <c r="E9" s="314"/>
+      <c r="F9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J9" s="314"/>
+      <c r="K9" s="314"/>
+      <c r="L9" s="77"/>
+      <c r="M9" s="314"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B10" s="315"/>
+      <c r="C10" s="315"/>
+      <c r="D10" s="315"/>
+      <c r="E10" s="315"/>
+      <c r="F10" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="J10" s="315"/>
+      <c r="K10" s="315"/>
+      <c r="L10" s="78"/>
+      <c r="M10" s="315"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B11" s="314"/>
+      <c r="C11" s="314"/>
+      <c r="D11" s="314"/>
+      <c r="E11" s="314"/>
+      <c r="F11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J11" s="314"/>
+      <c r="K11" s="314"/>
+      <c r="L11" s="77"/>
+      <c r="M11" s="314"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B12" s="315"/>
+      <c r="C12" s="315"/>
+      <c r="D12" s="315"/>
+      <c r="E12" s="315"/>
+      <c r="F12" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12" s="315"/>
+      <c r="K12" s="315"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="315"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B13" s="314"/>
+      <c r="C13" s="314"/>
+      <c r="D13" s="314"/>
+      <c r="E13" s="314"/>
+      <c r="F13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J13" s="314"/>
+      <c r="K13" s="314"/>
+      <c r="L13" s="77"/>
+      <c r="M13" s="314"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B14" s="315"/>
+      <c r="C14" s="315"/>
+      <c r="D14" s="315"/>
+      <c r="E14" s="315"/>
+      <c r="F14" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="J14" s="315"/>
+      <c r="K14" s="315"/>
+      <c r="L14" s="78"/>
+      <c r="M14" s="315"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M15" s="24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Menu!A1" display="menu"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="7169" r:id="rId4" name="Drop Down 1">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>876300</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="7170" r:id="rId5" name="Drop Down 2">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>15240</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>38100</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>891540</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="7171" r:id="rId6" name="Drop Down 3">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>7620</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>883920</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="7174" r:id="rId7" name="Drop Down 6">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>7620</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>30480</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>883920</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>22860</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -45661,7 +47578,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -45913,7 +47830,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -46503,399 +48420,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="14.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="5" width="13.33203125" customWidth="1"/>
-    <col min="10" max="10" width="37.77734375" customWidth="1"/>
-    <col min="11" max="12" width="13.21875" customWidth="1"/>
-    <col min="13" max="13" width="23.6640625" customWidth="1"/>
-    <col min="14" max="14" width="2.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F3" s="316"/>
-      <c r="G3" s="316"/>
-      <c r="H3" s="316"/>
-      <c r="I3" s="316"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F5" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F7" s="313" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7" s="313"/>
-      <c r="H7" s="313"/>
-      <c r="I7" s="313"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B8" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B9" s="314"/>
-      <c r="C9" s="314"/>
-      <c r="D9" s="314"/>
-      <c r="E9" s="314"/>
-      <c r="F9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J9" s="314"/>
-      <c r="K9" s="314"/>
-      <c r="L9" s="77"/>
-      <c r="M9" s="314"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B10" s="315"/>
-      <c r="C10" s="315"/>
-      <c r="D10" s="315"/>
-      <c r="E10" s="315"/>
-      <c r="F10" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="H10" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="I10" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="J10" s="315"/>
-      <c r="K10" s="315"/>
-      <c r="L10" s="78"/>
-      <c r="M10" s="315"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B11" s="314"/>
-      <c r="C11" s="314"/>
-      <c r="D11" s="314"/>
-      <c r="E11" s="314"/>
-      <c r="F11" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J11" s="314"/>
-      <c r="K11" s="314"/>
-      <c r="L11" s="77"/>
-      <c r="M11" s="314"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B12" s="315"/>
-      <c r="C12" s="315"/>
-      <c r="D12" s="315"/>
-      <c r="E12" s="315"/>
-      <c r="F12" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="G12" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="I12" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="J12" s="315"/>
-      <c r="K12" s="315"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="315"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B13" s="314"/>
-      <c r="C13" s="314"/>
-      <c r="D13" s="314"/>
-      <c r="E13" s="314"/>
-      <c r="F13" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J13" s="314"/>
-      <c r="K13" s="314"/>
-      <c r="L13" s="77"/>
-      <c r="M13" s="314"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B14" s="315"/>
-      <c r="C14" s="315"/>
-      <c r="D14" s="315"/>
-      <c r="E14" s="315"/>
-      <c r="F14" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="G14" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="H14" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="I14" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="J14" s="315"/>
-      <c r="K14" s="315"/>
-      <c r="L14" s="78"/>
-      <c r="M14" s="315"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M15" s="24" t="s">
-        <v>81</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Menu!A1" display="menu"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x14">
-      <controls>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="7169" r:id="rId4" name="Drop Down 1">
-              <controlPr defaultSize="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>876300</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>22860</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="7170" r:id="rId5" name="Drop Down 2">
-              <controlPr defaultSize="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>2</xdr:col>
-                    <xdr:colOff>15240</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>38100</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>2</xdr:col>
-                    <xdr:colOff>891540</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="7171" r:id="rId6" name="Drop Down 3">
-              <controlPr defaultSize="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>7620</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>883920</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>22860</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="7174" r:id="rId7" name="Drop Down 6">
-              <controlPr defaultSize="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>7620</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>883920</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>22860</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-      </controls>
-    </mc:Choice>
-  </mc:AlternateContent>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -47140,7 +48665,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -47608,7 +49133,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -47774,7 +49299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -47919,6 +49444,185 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C5" s="32" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D5" s="20"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="34"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C6" s="32" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D6" s="20"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="34"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C7" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="D7" s="20"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="34"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C8" s="32" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D8" s="20"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="34"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C9" s="32" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D9" s="20"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="34"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C10" s="32" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="34"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Menu!A1" display="Menu"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C5" s="32" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>523</v>
+      </c>
+      <c r="E5" s="33"/>
+      <c r="F5" s="34"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C6" s="32" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D6" s="347" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E6" s="33"/>
+      <c r="F6" s="34"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C7" s="32" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E7" s="33"/>
+      <c r="F7" s="34"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C8" s="32" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E8" s="33"/>
+      <c r="F8" s="34"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C9" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E9" s="33"/>
+      <c r="F9" s="34"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C10" s="32" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E10" s="33"/>
+      <c r="F10" s="34"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C11" s="32" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D11" s="347" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E11" s="33"/>
+      <c r="F11" s="34"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C12" s="32" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="34"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F14" s="73" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Menu!A1" display="Menu"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M13"/>
@@ -47955,10 +49659,10 @@
       <c r="M2" s="12"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F3" s="316"/>
-      <c r="G3" s="316"/>
-      <c r="H3" s="316"/>
-      <c r="I3" s="316"/>
+      <c r="F3" s="317"/>
+      <c r="G3" s="317"/>
+      <c r="H3" s="317"/>
+      <c r="I3" s="317"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
@@ -49156,13 +50860,35 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="M21:M22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
     <mergeCell ref="M17:M18"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="C19:C20"/>
@@ -49177,35 +50903,13 @@
     <mergeCell ref="E17:E18"/>
     <mergeCell ref="J17:J18"/>
     <mergeCell ref="K17:K18"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="M15:M16"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="K21:K22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Menu!A1" display="menu"/>
